--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918665</v>
+        <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656079</v>
+        <v>655797</v>
       </c>
       <c r="R2" t="n">
-        <v>7121699</v>
+        <v>7121726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,15 +757,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918053</v>
+        <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655797</v>
+        <v>656079</v>
       </c>
       <c r="R3" t="n">
-        <v>7121726</v>
+        <v>7121699</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,30 +873,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918056</v>
+        <v>126917778</v>
       </c>
       <c r="B4" t="n">
-        <v>5492</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,43 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656019</v>
+        <v>656101</v>
       </c>
       <c r="R4" t="n">
-        <v>7121699</v>
+        <v>7121718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,30 +974,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1017,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918054</v>
+        <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>78647</v>
+        <v>5492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,34 +1004,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655856</v>
+        <v>656019</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B6" t="n">
-        <v>78739</v>
+        <v>78678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,34 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R6" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1200,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,7 +1237,7 @@
         <v>126918060</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126917779</v>
       </c>
       <c r="B8" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R9" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,30 +1533,15 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1567,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1563,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R10" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,15 +1634,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>79569</v>
+        <v>97314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R11" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>97239</v>
+        <v>79600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R12" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1873,7 +1873,7 @@
         <v>126917824</v>
       </c>
       <c r="B13" t="n">
-        <v>77929</v>
+        <v>77989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>126920126</v>
       </c>
       <c r="B14" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>126918051</v>
       </c>
       <c r="B15" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>126918058</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917783</v>
+        <v>126917780</v>
       </c>
       <c r="B17" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655862</v>
+        <v>656003</v>
       </c>
       <c r="R17" t="n">
-        <v>7121762</v>
+        <v>7121751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918062</v>
+        <v>126917783</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655890</v>
+        <v>655862</v>
       </c>
       <c r="R18" t="n">
-        <v>7121804</v>
+        <v>7121762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,30 +2488,15 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2522,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126917780</v>
+        <v>126918703</v>
       </c>
       <c r="B19" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656003</v>
+        <v>656128</v>
       </c>
       <c r="R19" t="n">
-        <v>7121751</v>
+        <v>7121753</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,12 +2592,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2623,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918703</v>
+        <v>126918062</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2654,14 +2639,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656128</v>
+        <v>655890</v>
       </c>
       <c r="R20" t="n">
-        <v>7121753</v>
+        <v>7121804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,15 +2690,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917829</v>
+        <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78386</v>
+        <v>78678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656003</v>
+        <v>656038</v>
       </c>
       <c r="R22" t="n">
-        <v>7121751</v>
+        <v>7121659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917782</v>
+        <v>126917829</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>78417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655900</v>
+        <v>656003</v>
       </c>
       <c r="R23" t="n">
-        <v>7121770</v>
+        <v>7121751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3038,7 +3038,7 @@
         <v>126918702</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917821</v>
+        <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>78647</v>
+        <v>78770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656038</v>
+        <v>655900</v>
       </c>
       <c r="R25" t="n">
-        <v>7121659</v>
+        <v>7121770</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,7 +3240,7 @@
         <v>126917828</v>
       </c>
       <c r="B26" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>126918663</v>
       </c>
       <c r="B27" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918052</v>
+        <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>80955</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655794</v>
+        <v>655968</v>
       </c>
       <c r="R28" t="n">
-        <v>7121729</v>
+        <v>7121765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,30 +3521,15 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3555,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>80986</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,34 +3551,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R29" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,15 +3622,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3765,7 +3765,7 @@
         <v>126950488</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>126950487</v>
       </c>
       <c r="B32" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>126950490</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>126950489</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>126950492</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>126950485</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126950491</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>126950486</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R4" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,15 +974,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918056</v>
+        <v>126917778</v>
       </c>
       <c r="B5" t="n">
-        <v>5492</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,43 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656019</v>
+        <v>656101</v>
       </c>
       <c r="R5" t="n">
-        <v>7121699</v>
+        <v>7121718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,30 +1090,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1118,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918054</v>
+        <v>126918056</v>
       </c>
       <c r="B6" t="n">
-        <v>78678</v>
+        <v>5492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,34 +1120,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655856</v>
+        <v>656019</v>
       </c>
       <c r="R6" t="n">
-        <v>7121730</v>
+        <v>7121699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1237,7 +1237,7 @@
         <v>126918060</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126917779</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>97314</v>
+        <v>97320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126917824</v>
       </c>
       <c r="B13" t="n">
-        <v>77989</v>
+        <v>77992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>126920126</v>
       </c>
       <c r="B14" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>126918051</v>
       </c>
       <c r="B15" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>126918058</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917780</v>
+        <v>126918703</v>
       </c>
       <c r="B17" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656003</v>
+        <v>656128</v>
       </c>
       <c r="R17" t="n">
-        <v>7121751</v>
+        <v>7121753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,12 +2390,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126917783</v>
+        <v>126918062</v>
       </c>
       <c r="B18" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655862</v>
+        <v>655890</v>
       </c>
       <c r="R18" t="n">
-        <v>7121762</v>
+        <v>7121804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,15 +2488,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2507,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918703</v>
+        <v>126917780</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,21 +2533,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656128</v>
+        <v>656003</v>
       </c>
       <c r="R19" t="n">
-        <v>7121753</v>
+        <v>7121751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,12 +2607,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2608,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918062</v>
+        <v>126917783</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,34 +2634,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655890</v>
+        <v>655862</v>
       </c>
       <c r="R20" t="n">
-        <v>7121804</v>
+        <v>7121762</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,30 +2705,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917821</v>
+        <v>126918702</v>
       </c>
       <c r="B22" t="n">
-        <v>78678</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656038</v>
+        <v>656080</v>
       </c>
       <c r="R22" t="n">
-        <v>7121659</v>
+        <v>7121779</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,12 +2918,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917829</v>
+        <v>126917821</v>
       </c>
       <c r="B23" t="n">
-        <v>78417</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656003</v>
+        <v>656038</v>
       </c>
       <c r="R23" t="n">
-        <v>7121751</v>
+        <v>7121659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>78420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R24" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3139,7 +3139,7 @@
         <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126917828</v>
       </c>
       <c r="B26" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918663</v>
+        <v>126918052</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>80989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655853</v>
+        <v>655794</v>
       </c>
       <c r="R27" t="n">
-        <v>7121762</v>
+        <v>7121729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,15 +3420,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3442,7 +3457,7 @@
         <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918052</v>
+        <v>126918663</v>
       </c>
       <c r="B29" t="n">
-        <v>80986</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,34 +3566,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655794</v>
+        <v>655853</v>
       </c>
       <c r="R29" t="n">
-        <v>7121729</v>
+        <v>7121762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,30 +3637,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3765,7 +3765,7 @@
         <v>126950488</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>126950487</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>126950490</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>126950489</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>126950492</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>126950485</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126950491</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>126950486</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918053</v>
+        <v>126918665</v>
       </c>
       <c r="B2" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655797</v>
+        <v>656079</v>
       </c>
       <c r="R2" t="n">
-        <v>7121726</v>
+        <v>7121699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,30 +757,15 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918665</v>
+        <v>126918053</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,34 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>656079</v>
+        <v>655797</v>
       </c>
       <c r="R3" t="n">
-        <v>7121699</v>
+        <v>7121726</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,15 +858,30 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917778</v>
+        <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>5492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,34 +1019,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656101</v>
+        <v>656019</v>
       </c>
       <c r="R5" t="n">
-        <v>7121718</v>
+        <v>7121699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,15 +1099,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1109,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918056</v>
+        <v>126917778</v>
       </c>
       <c r="B6" t="n">
-        <v>5492</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,43 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656019</v>
+        <v>656101</v>
       </c>
       <c r="R6" t="n">
-        <v>7121699</v>
+        <v>7121718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,30 +1215,15 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R9" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,15 +1533,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1552,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R10" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,30 +1649,15 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R22" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2918,12 +2918,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917821</v>
+        <v>126918702</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656038</v>
+        <v>656080</v>
       </c>
       <c r="R23" t="n">
-        <v>7121659</v>
+        <v>7121779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917829</v>
+        <v>126917782</v>
       </c>
       <c r="B24" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656003</v>
+        <v>655900</v>
       </c>
       <c r="R24" t="n">
-        <v>7121751</v>
+        <v>7121770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917782</v>
+        <v>126917821</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655900</v>
+        <v>656038</v>
       </c>
       <c r="R25" t="n">
-        <v>7121770</v>
+        <v>7121659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918052</v>
+        <v>126917802</v>
       </c>
       <c r="B27" t="n">
-        <v>80989</v>
+        <v>80117</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655794</v>
+        <v>655968</v>
       </c>
       <c r="R27" t="n">
-        <v>7121729</v>
+        <v>7121765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,30 +3420,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3454,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>80989</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R28" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,15 +3521,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918665</v>
+        <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656079</v>
+        <v>655797</v>
       </c>
       <c r="R2" t="n">
-        <v>7121699</v>
+        <v>7121726</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,15 +757,30 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918053</v>
+        <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,34 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655797</v>
+        <v>656079</v>
       </c>
       <c r="R3" t="n">
-        <v>7121726</v>
+        <v>7121699</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,30 +873,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917829</v>
+        <v>126917782</v>
       </c>
       <c r="B22" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656003</v>
+        <v>655900</v>
       </c>
       <c r="R22" t="n">
-        <v>7121751</v>
+        <v>7121770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918702</v>
+        <v>126917821</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656080</v>
+        <v>656038</v>
       </c>
       <c r="R23" t="n">
-        <v>7121779</v>
+        <v>7121659</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917782</v>
+        <v>126917829</v>
       </c>
       <c r="B24" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655900</v>
+        <v>656003</v>
       </c>
       <c r="R24" t="n">
-        <v>7121770</v>
+        <v>7121751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917821</v>
+        <v>126918702</v>
       </c>
       <c r="B25" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656038</v>
+        <v>656080</v>
       </c>
       <c r="R25" t="n">
-        <v>7121659</v>
+        <v>7121779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,12 +3221,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R9" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,30 +1533,15 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1567,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1563,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R10" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,15 +1634,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B11" t="n">
-        <v>97320</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R11" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B12" t="n">
-        <v>79603</v>
+        <v>97321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R12" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B24" t="n">
-        <v>78420</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R24" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R25" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,12 +3221,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B27" t="n">
-        <v>80117</v>
+        <v>80989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R27" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,15 +3420,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3439,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918052</v>
+        <v>126918663</v>
       </c>
       <c r="B28" t="n">
-        <v>80989</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,34 +3465,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655794</v>
+        <v>655853</v>
       </c>
       <c r="R28" t="n">
-        <v>7121729</v>
+        <v>7121762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,30 +3536,15 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918663</v>
+        <v>126917802</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655853</v>
+        <v>655968</v>
       </c>
       <c r="R29" t="n">
-        <v>7121762</v>
+        <v>7121765</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3640,12 +3640,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918054</v>
+        <v>126917778</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655856</v>
+        <v>656101</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,30 +974,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918056</v>
+        <v>126918054</v>
       </c>
       <c r="B5" t="n">
-        <v>5492</v>
+        <v>78681</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,43 +1004,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656019</v>
+        <v>655856</v>
       </c>
       <c r="R5" t="n">
-        <v>7121699</v>
+        <v>7121730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917778</v>
+        <v>126918056</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>5492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,34 +1120,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656101</v>
+        <v>656019</v>
       </c>
       <c r="R6" t="n">
-        <v>7121718</v>
+        <v>7121699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1200,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>97321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R11" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>97321</v>
+        <v>79603</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R12" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R4" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,15 +974,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918054</v>
+        <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>78681</v>
+        <v>5492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,34 +1019,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655856</v>
+        <v>656019</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918056</v>
+        <v>126917778</v>
       </c>
       <c r="B6" t="n">
-        <v>5492</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,43 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656019</v>
+        <v>656101</v>
       </c>
       <c r="R6" t="n">
-        <v>7121699</v>
+        <v>7121718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,30 +1215,15 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B11" t="n">
-        <v>97321</v>
+        <v>79603</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R11" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B12" t="n">
-        <v>79603</v>
+        <v>97321</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R12" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917782</v>
+        <v>126917829</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>78420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655900</v>
+        <v>656003</v>
       </c>
       <c r="R22" t="n">
-        <v>7121770</v>
+        <v>7121751</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917821</v>
+        <v>126918702</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656038</v>
+        <v>656080</v>
       </c>
       <c r="R23" t="n">
-        <v>7121659</v>
+        <v>7121779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126918702</v>
+        <v>126917821</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656080</v>
+        <v>656038</v>
       </c>
       <c r="R24" t="n">
-        <v>7121779</v>
+        <v>7121659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917829</v>
+        <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>78420</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656003</v>
+        <v>655900</v>
       </c>
       <c r="R25" t="n">
-        <v>7121751</v>
+        <v>7121770</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918703</v>
+        <v>126917780</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656128</v>
+        <v>656003</v>
       </c>
       <c r="R17" t="n">
-        <v>7121753</v>
+        <v>7121751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,12 +2390,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918062</v>
+        <v>126917783</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655890</v>
+        <v>655862</v>
       </c>
       <c r="R18" t="n">
-        <v>7121804</v>
+        <v>7121762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,30 +2488,15 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2522,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126917780</v>
+        <v>126918703</v>
       </c>
       <c r="B19" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656003</v>
+        <v>656128</v>
       </c>
       <c r="R19" t="n">
-        <v>7121751</v>
+        <v>7121753</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,12 +2592,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2623,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126917783</v>
+        <v>126918062</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,34 +2619,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655862</v>
+        <v>655890</v>
       </c>
       <c r="R20" t="n">
-        <v>7121762</v>
+        <v>7121804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,15 +2690,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917829</v>
+        <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656003</v>
+        <v>656038</v>
       </c>
       <c r="R22" t="n">
-        <v>7121751</v>
+        <v>7121659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>78420</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R23" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917821</v>
+        <v>126918702</v>
       </c>
       <c r="B24" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656038</v>
+        <v>656080</v>
       </c>
       <c r="R24" t="n">
-        <v>7121659</v>
+        <v>7121779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3454,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918663</v>
+        <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>80117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,21 +3465,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655853</v>
+        <v>655968</v>
       </c>
       <c r="R28" t="n">
-        <v>7121762</v>
+        <v>7121765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,12 +3539,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126917802</v>
+        <v>126918663</v>
       </c>
       <c r="B29" t="n">
-        <v>80117</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655968</v>
+        <v>655853</v>
       </c>
       <c r="R29" t="n">
-        <v>7121765</v>
+        <v>7121762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3640,12 +3640,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>126917778</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>126918060</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126917779</v>
       </c>
       <c r="B8" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R9" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,15 +1533,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1552,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B10" t="n">
-        <v>80117</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R10" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,30 +1649,15 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1671,7 +1671,7 @@
         <v>126917769</v>
       </c>
       <c r="B11" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126920124</v>
       </c>
       <c r="B12" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126917824</v>
       </c>
       <c r="B13" t="n">
-        <v>77992</v>
+        <v>77996</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>126920126</v>
       </c>
       <c r="B14" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>126918051</v>
       </c>
       <c r="B15" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>126918058</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917780</v>
+        <v>126918062</v>
       </c>
       <c r="B17" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,34 +2316,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656003</v>
+        <v>655890</v>
       </c>
       <c r="R17" t="n">
-        <v>7121751</v>
+        <v>7121804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,15 +2387,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2406,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126917783</v>
+        <v>126917780</v>
       </c>
       <c r="B18" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,10 +2456,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655862</v>
+        <v>656003</v>
       </c>
       <c r="R18" t="n">
-        <v>7121762</v>
+        <v>7121751</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2507,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918703</v>
+        <v>126917783</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,21 +2533,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656128</v>
+        <v>655862</v>
       </c>
       <c r="R19" t="n">
-        <v>7121753</v>
+        <v>7121762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,12 +2607,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2608,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918062</v>
+        <v>126918703</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2639,14 +2654,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655890</v>
+        <v>656128</v>
       </c>
       <c r="R20" t="n">
-        <v>7121804</v>
+        <v>7121753</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,30 +2705,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,7 +2727,7 @@
         <v>126917773</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917821</v>
+        <v>126917829</v>
       </c>
       <c r="B22" t="n">
-        <v>78681</v>
+        <v>78424</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656038</v>
+        <v>656003</v>
       </c>
       <c r="R22" t="n">
-        <v>7121659</v>
+        <v>7121751</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B23" t="n">
-        <v>78420</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R23" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126918702</v>
+        <v>126917782</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656080</v>
+        <v>655900</v>
       </c>
       <c r="R24" t="n">
-        <v>7121779</v>
+        <v>7121770</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917782</v>
+        <v>126917821</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655900</v>
+        <v>656038</v>
       </c>
       <c r="R25" t="n">
-        <v>7121770</v>
+        <v>7121659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,7 +3240,7 @@
         <v>126917828</v>
       </c>
       <c r="B26" t="n">
-        <v>78420</v>
+        <v>78424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918052</v>
+        <v>126917802</v>
       </c>
       <c r="B27" t="n">
-        <v>80989</v>
+        <v>80121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655794</v>
+        <v>655968</v>
       </c>
       <c r="R27" t="n">
-        <v>7121729</v>
+        <v>7121765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,30 +3420,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3454,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>80993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R28" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,15 +3521,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3558,7 +3558,7 @@
         <v>126918663</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>126918661</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>126950488</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>126950487</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>126950490</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>126950489</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>126950492</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>126950485</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126950491</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>126950486</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918054</v>
+        <v>126917778</v>
       </c>
       <c r="B4" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655856</v>
+        <v>656101</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,30 +974,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1008,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918056</v>
+        <v>126918054</v>
       </c>
       <c r="B5" t="n">
-        <v>5493</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,43 +1004,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656019</v>
+        <v>655856</v>
       </c>
       <c r="R5" t="n">
-        <v>7121699</v>
+        <v>7121730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917778</v>
+        <v>126918056</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>5493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,34 +1120,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>101410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656101</v>
+        <v>656019</v>
       </c>
       <c r="R6" t="n">
-        <v>7121718</v>
+        <v>7121699</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1200,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R9" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,30 +1533,15 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1567,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1563,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R10" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,15 +1634,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>79607</v>
+        <v>97325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R11" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>97325</v>
+        <v>79607</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R12" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918062</v>
+        <v>126918703</v>
       </c>
       <c r="B17" t="n">
         <v>79018</v>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655890</v>
+        <v>656128</v>
       </c>
       <c r="R17" t="n">
-        <v>7121804</v>
+        <v>7121753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,30 +2387,15 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2421,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126917780</v>
+        <v>126918062</v>
       </c>
       <c r="B18" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2432,34 +2417,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656003</v>
+        <v>655890</v>
       </c>
       <c r="R18" t="n">
-        <v>7121751</v>
+        <v>7121804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,15 +2488,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2522,7 +2522,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126917783</v>
+        <v>126917780</v>
       </c>
       <c r="B19" t="n">
         <v>78777</v>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655862</v>
+        <v>656003</v>
       </c>
       <c r="R19" t="n">
-        <v>7121762</v>
+        <v>7121751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918703</v>
+        <v>126917783</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656128</v>
+        <v>655862</v>
       </c>
       <c r="R20" t="n">
-        <v>7121753</v>
+        <v>7121762</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2708,12 +2708,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917829</v>
+        <v>126917782</v>
       </c>
       <c r="B22" t="n">
-        <v>78424</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656003</v>
+        <v>655900</v>
       </c>
       <c r="R22" t="n">
-        <v>7121751</v>
+        <v>7121770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917782</v>
+        <v>126917829</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>78424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655900</v>
+        <v>656003</v>
       </c>
       <c r="R24" t="n">
-        <v>7121770</v>
+        <v>7121751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B27" t="n">
-        <v>80121</v>
+        <v>80993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R27" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,15 +3420,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3439,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918052</v>
+        <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>80993</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,34 +3465,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655794</v>
+        <v>655968</v>
       </c>
       <c r="R28" t="n">
-        <v>7121729</v>
+        <v>7121765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,30 +3536,15 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R4" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,15 +974,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -993,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918054</v>
+        <v>126917778</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,34 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655856</v>
+        <v>656101</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121718</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,30 +1090,15 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917782</v>
+        <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655900</v>
+        <v>656038</v>
       </c>
       <c r="R22" t="n">
-        <v>7121770</v>
+        <v>7121659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R23" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B24" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R24" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917821</v>
+        <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656038</v>
+        <v>655900</v>
       </c>
       <c r="R25" t="n">
-        <v>7121659</v>
+        <v>7121770</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918052</v>
+        <v>126918663</v>
       </c>
       <c r="B27" t="n">
-        <v>80993</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655794</v>
+        <v>655853</v>
       </c>
       <c r="R27" t="n">
-        <v>7121729</v>
+        <v>7121762</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,30 +3420,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3454,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>80993</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,34 +3450,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R28" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3536,15 +3521,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918663</v>
+        <v>126917802</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655853</v>
+        <v>655968</v>
       </c>
       <c r="R29" t="n">
-        <v>7121762</v>
+        <v>7121765</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3640,12 +3640,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917821</v>
+        <v>126917782</v>
       </c>
       <c r="B22" t="n">
-        <v>78685</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656038</v>
+        <v>655900</v>
       </c>
       <c r="R22" t="n">
-        <v>7121659</v>
+        <v>7121770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B23" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R23" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78424</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R24" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917782</v>
+        <v>126917821</v>
       </c>
       <c r="B25" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655900</v>
+        <v>656038</v>
       </c>
       <c r="R25" t="n">
-        <v>7121770</v>
+        <v>7121659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918054</v>
+        <v>126918056</v>
       </c>
       <c r="B4" t="n">
-        <v>78685</v>
+        <v>5493</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655856</v>
+        <v>656019</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121699</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,34 +1028,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R5" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1090,15 +1099,30 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1109,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918056</v>
+        <v>126917778</v>
       </c>
       <c r="B6" t="n">
-        <v>5493</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,43 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101410</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656019</v>
+        <v>656101</v>
       </c>
       <c r="R6" t="n">
-        <v>7121699</v>
+        <v>7121718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,30 +1215,15 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R9" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,15 +1533,30 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1552,10 +1567,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1563,34 +1578,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R10" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1634,30 +1649,15 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917782</v>
+        <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>78685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655900</v>
+        <v>656038</v>
       </c>
       <c r="R22" t="n">
-        <v>7121770</v>
+        <v>7121659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918702</v>
+        <v>126917782</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656080</v>
+        <v>655900</v>
       </c>
       <c r="R23" t="n">
-        <v>7121779</v>
+        <v>7121770</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126917821</v>
+        <v>126918702</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656038</v>
+        <v>656080</v>
       </c>
       <c r="R25" t="n">
-        <v>7121659</v>
+        <v>7121779</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,12 +3221,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918056</v>
+        <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>5493</v>
+        <v>78685</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,43 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656019</v>
+        <v>655856</v>
       </c>
       <c r="R4" t="n">
-        <v>7121699</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918054</v>
+        <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>78685</v>
+        <v>5493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,34 +1019,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655856</v>
+        <v>656019</v>
       </c>
       <c r="R5" t="n">
-        <v>7121730</v>
+        <v>7121699</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918055</v>
+        <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,34 +1462,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655875</v>
+        <v>656095</v>
       </c>
       <c r="R9" t="n">
-        <v>7121716</v>
+        <v>7121717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,30 +1533,15 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1567,10 +1552,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126917819</v>
+        <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,34 +1563,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656095</v>
+        <v>655875</v>
       </c>
       <c r="R10" t="n">
-        <v>7121717</v>
+        <v>7121716</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,15 +1634,30 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918663</v>
+        <v>126918052</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>80993</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655853</v>
+        <v>655794</v>
       </c>
       <c r="R27" t="n">
-        <v>7121762</v>
+        <v>7121729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,15 +3420,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3439,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918052</v>
+        <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>80993</v>
+        <v>80121</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,34 +3465,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655794</v>
+        <v>655968</v>
       </c>
       <c r="R28" t="n">
-        <v>7121729</v>
+        <v>7121765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3521,30 +3536,15 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126917802</v>
+        <v>126918663</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,21 +3566,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3590,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655968</v>
+        <v>655853</v>
       </c>
       <c r="R29" t="n">
-        <v>7121765</v>
+        <v>7121762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3640,12 +3640,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>126917778</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>126918060</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126917779</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B11" t="n">
-        <v>97325</v>
+        <v>79609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R11" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B12" t="n">
-        <v>79607</v>
+        <v>97327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R12" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1873,7 +1873,7 @@
         <v>126917824</v>
       </c>
       <c r="B13" t="n">
-        <v>77996</v>
+        <v>77998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>126920126</v>
       </c>
       <c r="B14" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>126918051</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>126918058</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918703</v>
+        <v>126918062</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656128</v>
+        <v>655890</v>
       </c>
       <c r="R17" t="n">
-        <v>7121753</v>
+        <v>7121804</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,15 +2387,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2406,10 +2421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918062</v>
+        <v>126918703</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2437,14 +2452,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655890</v>
+        <v>656128</v>
       </c>
       <c r="R18" t="n">
-        <v>7121804</v>
+        <v>7121753</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,30 +2503,15 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2525,7 +2525,7 @@
         <v>126917780</v>
       </c>
       <c r="B19" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>126917783</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>126917773</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917821</v>
+        <v>126917782</v>
       </c>
       <c r="B22" t="n">
-        <v>78685</v>
+        <v>78779</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>656038</v>
+        <v>655900</v>
       </c>
       <c r="R22" t="n">
-        <v>7121659</v>
+        <v>7121770</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917782</v>
+        <v>126917829</v>
       </c>
       <c r="B23" t="n">
-        <v>78777</v>
+        <v>78426</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655900</v>
+        <v>656003</v>
       </c>
       <c r="R23" t="n">
-        <v>7121770</v>
+        <v>7121751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917829</v>
+        <v>126917821</v>
       </c>
       <c r="B24" t="n">
-        <v>78424</v>
+        <v>78687</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656003</v>
+        <v>656038</v>
       </c>
       <c r="R24" t="n">
-        <v>7121751</v>
+        <v>7121659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3139,7 +3139,7 @@
         <v>126918702</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126917828</v>
       </c>
       <c r="B26" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918052</v>
+        <v>126917802</v>
       </c>
       <c r="B27" t="n">
-        <v>80993</v>
+        <v>80123</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655794</v>
+        <v>655968</v>
       </c>
       <c r="R27" t="n">
-        <v>7121729</v>
+        <v>7121765</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,30 +3420,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3454,10 +3439,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126917802</v>
+        <v>126918663</v>
       </c>
       <c r="B28" t="n">
-        <v>80121</v>
+        <v>78779</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3465,21 +3450,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3489,10 +3474,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655968</v>
+        <v>655853</v>
       </c>
       <c r="R28" t="n">
-        <v>7121765</v>
+        <v>7121762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3539,12 +3524,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3555,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918663</v>
+        <v>126918052</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>80995</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,34 +3551,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655853</v>
+        <v>655794</v>
       </c>
       <c r="R29" t="n">
-        <v>7121762</v>
+        <v>7121729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,15 +3622,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3659,7 +3659,7 @@
         <v>126918661</v>
       </c>
       <c r="B30" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>126950488</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>126950487</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>126950490</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>126950489</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>126950492</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>126950485</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126950491</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>126950486</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -1668,32 +1668,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126917769</v>
+        <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>79609</v>
+        <v>97327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655885</v>
+        <v>656103</v>
       </c>
       <c r="R11" t="n">
-        <v>7121658</v>
+        <v>7121715</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,12 +1753,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Peter Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1769,32 +1769,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126920124</v>
+        <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>97327</v>
+        <v>79609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656103</v>
+        <v>655885</v>
       </c>
       <c r="R12" t="n">
-        <v>7121715</v>
+        <v>7121658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1854,12 +1854,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Andersson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918062</v>
+        <v>126918703</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2336,14 +2336,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655890</v>
+        <v>656128</v>
       </c>
       <c r="R17" t="n">
-        <v>7121804</v>
+        <v>7121753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2387,30 +2387,15 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2421,7 +2406,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918703</v>
+        <v>126918062</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2452,14 +2437,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>656128</v>
+        <v>655890</v>
       </c>
       <c r="R18" t="n">
-        <v>7121753</v>
+        <v>7121804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2503,15 +2488,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2833,10 +2833,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126917782</v>
+        <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78779</v>
+        <v>78687</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2844,21 +2844,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655900</v>
+        <v>656038</v>
       </c>
       <c r="R22" t="n">
-        <v>7121770</v>
+        <v>7121659</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B23" t="n">
-        <v>78426</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R23" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917821</v>
+        <v>126917829</v>
       </c>
       <c r="B24" t="n">
-        <v>78687</v>
+        <v>78426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656038</v>
+        <v>656003</v>
       </c>
       <c r="R24" t="n">
-        <v>7121659</v>
+        <v>7121751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3136,10 +3136,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126918702</v>
+        <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3147,21 +3147,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656080</v>
+        <v>655900</v>
       </c>
       <c r="R25" t="n">
-        <v>7121779</v>
+        <v>7121770</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3221,12 +3221,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126917802</v>
+        <v>126918052</v>
       </c>
       <c r="B27" t="n">
-        <v>80123</v>
+        <v>80995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655968</v>
+        <v>655794</v>
       </c>
       <c r="R27" t="n">
-        <v>7121765</v>
+        <v>7121729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,15 +3420,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3439,10 +3454,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918663</v>
+        <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>78779</v>
+        <v>80123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3450,21 +3465,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3474,10 +3489,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655853</v>
+        <v>655968</v>
       </c>
       <c r="R28" t="n">
-        <v>7121762</v>
+        <v>7121765</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3524,12 +3539,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3540,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918052</v>
+        <v>126918663</v>
       </c>
       <c r="B29" t="n">
-        <v>80995</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,34 +3566,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655794</v>
+        <v>655853</v>
       </c>
       <c r="R29" t="n">
-        <v>7121729</v>
+        <v>7121762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,30 +3637,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4568,6 +4568,536 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129688147</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78828</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norrfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>655618</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7121802</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129688146</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78829</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norrfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>655621</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7121797</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129688525</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92864</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norrfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655601</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7121816</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129688148</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92902</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norrfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>655672</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7121837</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129688145</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79661</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norrfors, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655795</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7121764</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78829</v>
+        <v>78833</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92864</v>
+        <v>92869</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92902</v>
+        <v>92907</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79661</v>
+        <v>79665</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B39" t="n">
-        <v>78832</v>
+        <v>78834</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R39" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B40" t="n">
         <v>78833</v>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R40" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B41" t="n">
-        <v>92869</v>
+        <v>92908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R41" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B42" t="n">
-        <v>92907</v>
+        <v>92870</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R42" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79665</v>
+        <v>79666</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78834</v>
+        <v>78838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R39" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78833</v>
+        <v>78839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R40" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92908</v>
+        <v>92875</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R41" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92870</v>
+        <v>92913</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R42" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79666</v>
+        <v>79671</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B39" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R39" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B40" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R40" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B41" t="n">
-        <v>92875</v>
+        <v>92913</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R41" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B42" t="n">
-        <v>92913</v>
+        <v>92875</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R42" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92913</v>
+        <v>92875</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R41" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92875</v>
+        <v>92913</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R42" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R39" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R40" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B39" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R39" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B40" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R40" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4785,7 +4785,7 @@
         <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92913</v>
+        <v>92917</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R39" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R40" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B41" t="n">
-        <v>92879</v>
+        <v>92919</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R41" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B42" t="n">
-        <v>92917</v>
+        <v>92881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R42" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92919</v>
+        <v>92881</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R41" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92881</v>
+        <v>92919</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R42" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B41" t="n">
-        <v>92881</v>
+        <v>92919</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R41" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B42" t="n">
-        <v>92919</v>
+        <v>92881</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R42" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B39" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R39" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B40" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R40" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92919</v>
+        <v>92884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R41" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92881</v>
+        <v>92922</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R42" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78842</v>
+        <v>78841</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R39" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R40" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92922</v>
+        <v>92925</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4573,7 +4573,7 @@
         <v>129688147</v>
       </c>
       <c r="B39" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
         <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4785,7 +4785,7 @@
         <v>129688525</v>
       </c>
       <c r="B41" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         <v>129688148</v>
       </c>
       <c r="B42" t="n">
-        <v>92925</v>
+        <v>92926</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,10 +4570,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B39" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R39" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B40" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R40" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -4570,7 +4570,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129688146</v>
+        <v>129688147</v>
       </c>
       <c r="B39" t="n">
         <v>78846</v>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4609,10 +4609,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655621</v>
+        <v>655618</v>
       </c>
       <c r="R39" t="n">
-        <v>7121797</v>
+        <v>7121802</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,10 +4676,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129688147</v>
+        <v>129688146</v>
       </c>
       <c r="B40" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4687,21 +4687,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655618</v>
+        <v>655621</v>
       </c>
       <c r="R40" t="n">
-        <v>7121802</v>
+        <v>7121797</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4782,32 +4782,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129688525</v>
+        <v>129688148</v>
       </c>
       <c r="B41" t="n">
-        <v>92888</v>
+        <v>92943</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4821,10 +4821,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655601</v>
+        <v>655672</v>
       </c>
       <c r="R41" t="n">
-        <v>7121816</v>
+        <v>7121837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4888,32 +4888,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129688148</v>
+        <v>129688525</v>
       </c>
       <c r="B42" t="n">
-        <v>92926</v>
+        <v>92905</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655672</v>
+        <v>655601</v>
       </c>
       <c r="R42" t="n">
-        <v>7121837</v>
+        <v>7121816</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4997,7 +4997,7 @@
         <v>129688145</v>
       </c>
       <c r="B43" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918054</v>
+        <v>126917778</v>
       </c>
       <c r="B4" t="n">
-        <v>78687</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655856</v>
+        <v>656101</v>
       </c>
       <c r="R4" t="n">
-        <v>7121730</v>
+        <v>7121718</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,30 +974,15 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1011,7 +996,7 @@
         <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>5493</v>
+        <v>5492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>78678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,34 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R6" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,15 +1200,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,7 +1237,7 @@
         <v>126918060</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126917779</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>97327</v>
+        <v>97314</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126917824</v>
       </c>
       <c r="B13" t="n">
-        <v>77998</v>
+        <v>77989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>126920126</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>126918051</v>
       </c>
       <c r="B15" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>126918058</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918703</v>
+        <v>126917780</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656128</v>
+        <v>656003</v>
       </c>
       <c r="R17" t="n">
-        <v>7121753</v>
+        <v>7121751</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,12 +2390,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918062</v>
+        <v>126917783</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655890</v>
+        <v>655862</v>
       </c>
       <c r="R18" t="n">
-        <v>7121804</v>
+        <v>7121762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,30 +2488,15 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2522,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126917780</v>
+        <v>126918703</v>
       </c>
       <c r="B19" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2533,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2557,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656003</v>
+        <v>656128</v>
       </c>
       <c r="R19" t="n">
-        <v>7121751</v>
+        <v>7121753</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2607,12 +2592,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2623,10 +2608,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126917783</v>
+        <v>126918062</v>
       </c>
       <c r="B20" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,34 +2619,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655862</v>
+        <v>655890</v>
       </c>
       <c r="R20" t="n">
-        <v>7121762</v>
+        <v>7121804</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2705,15 +2690,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,7 +2727,7 @@
         <v>126917773</v>
       </c>
       <c r="B21" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>78417</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R23" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B24" t="n">
-        <v>78426</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R24" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3139,7 +3139,7 @@
         <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126917828</v>
       </c>
       <c r="B26" t="n">
-        <v>78426</v>
+        <v>78417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918052</v>
+        <v>126918663</v>
       </c>
       <c r="B27" t="n">
-        <v>80995</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655794</v>
+        <v>655853</v>
       </c>
       <c r="R27" t="n">
-        <v>7121729</v>
+        <v>7121762</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,30 +3420,15 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3457,7 +3442,7 @@
         <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3555,10 +3540,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918663</v>
+        <v>126918052</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>80986</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,34 +3551,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655853</v>
+        <v>655794</v>
       </c>
       <c r="R29" t="n">
-        <v>7121762</v>
+        <v>7121729</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3637,15 +3622,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3659,7 +3659,7 @@
         <v>126918661</v>
       </c>
       <c r="B30" t="n">
-        <v>57663</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>126950488</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>126950487</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>126950490</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>126950489</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>126950492</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>126950485</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126950491</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>126950486</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 1820-2021 artfynd.xlsx
+++ b/artfynd/A 1820-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126918053</v>
       </c>
       <c r="B2" t="n">
-        <v>78678</v>
+        <v>78687</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>126918665</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126917778</v>
+        <v>126918054</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>78687</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,34 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>656101</v>
+        <v>655856</v>
       </c>
       <c r="R4" t="n">
-        <v>7121718</v>
+        <v>7121730</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,15 +974,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -996,7 +1011,7 @@
         <v>126918056</v>
       </c>
       <c r="B5" t="n">
-        <v>5492</v>
+        <v>5493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126918054</v>
+        <v>126917778</v>
       </c>
       <c r="B6" t="n">
-        <v>78678</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,34 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655856</v>
+        <v>656101</v>
       </c>
       <c r="R6" t="n">
-        <v>7121730</v>
+        <v>7121718</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,30 +1215,15 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1237,7 +1237,7 @@
         <v>126918060</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>126917779</v>
       </c>
       <c r="B8" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126917819</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>126918055</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>126920124</v>
       </c>
       <c r="B11" t="n">
-        <v>97314</v>
+        <v>97327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>126917769</v>
       </c>
       <c r="B12" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>126917824</v>
       </c>
       <c r="B13" t="n">
-        <v>77989</v>
+        <v>77998</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>126920126</v>
       </c>
       <c r="B14" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>126918051</v>
       </c>
       <c r="B15" t="n">
-        <v>79600</v>
+        <v>79609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         <v>126918058</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126917780</v>
+        <v>126918703</v>
       </c>
       <c r="B17" t="n">
-        <v>78770</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2316,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656003</v>
+        <v>656128</v>
       </c>
       <c r="R17" t="n">
-        <v>7121751</v>
+        <v>7121753</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2390,12 +2390,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126917783</v>
+        <v>126918062</v>
       </c>
       <c r="B18" t="n">
-        <v>78770</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,34 +2417,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655862</v>
+        <v>655890</v>
       </c>
       <c r="R18" t="n">
-        <v>7121762</v>
+        <v>7121804</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2488,15 +2488,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2507,10 +2522,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918703</v>
+        <v>126917780</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>78779</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2518,21 +2533,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2557,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656128</v>
+        <v>656003</v>
       </c>
       <c r="R19" t="n">
-        <v>7121753</v>
+        <v>7121751</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,12 +2607,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2608,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918062</v>
+        <v>126917783</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>78779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,34 +2634,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655890</v>
+        <v>655862</v>
       </c>
       <c r="R20" t="n">
-        <v>7121804</v>
+        <v>7121762</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2690,30 +2705,15 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2727,7 +2727,7 @@
         <v>126917773</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
         <v>126917821</v>
       </c>
       <c r="B22" t="n">
-        <v>78678</v>
+        <v>78687</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126917829</v>
+        <v>126918702</v>
       </c>
       <c r="B23" t="n">
-        <v>78417</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2945,21 +2945,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>656003</v>
+        <v>656080</v>
       </c>
       <c r="R23" t="n">
-        <v>7121751</v>
+        <v>7121779</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3019,12 +3019,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3035,10 +3035,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126918702</v>
+        <v>126917829</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>78426</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3046,21 +3046,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>656080</v>
+        <v>656003</v>
       </c>
       <c r="R24" t="n">
-        <v>7121779</v>
+        <v>7121751</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,12 +3120,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -3139,7 +3139,7 @@
         <v>126917782</v>
       </c>
       <c r="B25" t="n">
-        <v>78770</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>126917828</v>
       </c>
       <c r="B26" t="n">
-        <v>78417</v>
+        <v>78426</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3338,10 +3338,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918663</v>
+        <v>126918052</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>80995</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3349,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Baksjökullen, Ås lm</t>
+          <t>Norrfors, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655853</v>
+        <v>655794</v>
       </c>
       <c r="R27" t="n">
-        <v>7121762</v>
+        <v>7121729</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3420,15 +3420,30 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3442,7 +3457,7 @@
         <v>126917802</v>
       </c>
       <c r="B28" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,10 +3555,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126918052</v>
+        <v>126918663</v>
       </c>
       <c r="B29" t="n">
-        <v>80986</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3551,34 +3566,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Norrfors, Ås lm</t>
+          <t>Baksjökullen, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655794</v>
+        <v>655853</v>
       </c>
       <c r="R29" t="n">
-        <v>7121729</v>
+        <v>7121762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,30 +3637,15 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carl Jansson, Nicklas Gustavsson, Peder Winding, Lisa Requin, Rolf Nylinder, Lise Mortensen, Gunilla R Burke, Jennica Andersson, kristina stenmarck, Miriam Schenk, Klas Magnusson, Anders Heggestad, Elke Blöhbaum, Beke Regelin, Elin Kannerby, Torbjörn Söderquist</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3659,7 +3659,7 @@
         <v>126918661</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57663</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>126950488</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>126950487</v>
       </c>
       <c r="B32" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>126950490</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>126950489</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
         <v>126950492</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>126950485</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
         <v>126950491</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>126950486</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
